--- a/indexes/nc_build_all/clean_type.xlsx
+++ b/indexes/nc_build_all/clean_type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\maximilien\adresse\magisnc-dinum-api-adresses-f752eef9c72d\magisnc-dinum-api-adresses-f752eef9c72d\indexes\nc_build_all\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BAPA\projets\DINUM\2025_API_ADRESSE\code\magis-dinum-api-adresses\indexes\nc_build_all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82E95946-33D6-4EF0-9CEB-04143336E3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A46E2F-C9D0-44A5-B79A-CFDB3126CC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="18420" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{D8778F9B-E95D-470A-9CFB-6343D998165F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8778F9B-E95D-470A-9CFB-6343D998165F}"/>
   </bookViews>
   <sheets>
     <sheet name="clean_type" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="264">
   <si>
     <t>type</t>
   </si>
@@ -212,9 +215,6 @@
     <t>Cequestre</t>
   </si>
   <si>
-    <t xml:space="preserve">Centre équestre </t>
-  </si>
-  <si>
     <t>Cformation</t>
   </si>
   <si>
@@ -581,9 +581,6 @@
     <t>Muscu</t>
   </si>
   <si>
-    <t xml:space="preserve">Musculation </t>
-  </si>
-  <si>
     <t>Musee</t>
   </si>
   <si>
@@ -825,6 +822,15 @@
   </si>
   <si>
     <t>Zoo</t>
+  </si>
+  <si>
+    <t>Tribu</t>
+  </si>
+  <si>
+    <t>Musculation</t>
+  </si>
+  <si>
+    <t>Centre équestre</t>
   </si>
 </sst>
 </file>
@@ -1196,8 +1202,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459D258D-C834-45E4-A6F3-F6CDD16D3540}">
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1484,951 +1494,959 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
         <v>59</v>
-      </c>
-      <c r="B37" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" t="s">
         <v>61</v>
-      </c>
-      <c r="B38" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
         <v>63</v>
-      </c>
-      <c r="B39" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
         <v>65</v>
-      </c>
-      <c r="B40" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" t="s">
         <v>67</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" t="s">
         <v>69</v>
-      </c>
-      <c r="B42" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
         <v>71</v>
-      </c>
-      <c r="B43" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" t="s">
         <v>73</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
         <v>75</v>
-      </c>
-      <c r="B45" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" t="s">
         <v>77</v>
-      </c>
-      <c r="B46" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
         <v>79</v>
-      </c>
-      <c r="B47" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" t="s">
         <v>82</v>
-      </c>
-      <c r="B49" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
         <v>84</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" t="s">
         <v>86</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
         <v>88</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" t="s">
         <v>91</v>
-      </c>
-      <c r="B54" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" t="s">
         <v>93</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" t="s">
         <v>95</v>
-      </c>
-      <c r="B56" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" t="s">
         <v>97</v>
-      </c>
-      <c r="B57" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
         <v>100</v>
-      </c>
-      <c r="B59" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>101</v>
+      </c>
+      <c r="B60" t="s">
         <v>102</v>
-      </c>
-      <c r="B60" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" t="s">
         <v>104</v>
-      </c>
-      <c r="B61" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>105</v>
+      </c>
+      <c r="B62" t="s">
         <v>106</v>
-      </c>
-      <c r="B62" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" t="s">
         <v>108</v>
-      </c>
-      <c r="B63" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" t="s">
         <v>110</v>
-      </c>
-      <c r="B64" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" t="s">
         <v>112</v>
-      </c>
-      <c r="B65" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
         <v>114</v>
-      </c>
-      <c r="B66" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" t="s">
         <v>116</v>
-      </c>
-      <c r="B67" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s">
         <v>118</v>
-      </c>
-      <c r="B68" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" t="s">
         <v>120</v>
-      </c>
-      <c r="B69" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" t="s">
         <v>122</v>
-      </c>
-      <c r="B70" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
         <v>124</v>
-      </c>
-      <c r="B71" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" t="s">
         <v>126</v>
-      </c>
-      <c r="B72" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" t="s">
         <v>128</v>
-      </c>
-      <c r="B73" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
         <v>130</v>
-      </c>
-      <c r="B74" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" t="s">
         <v>132</v>
-      </c>
-      <c r="B75" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>133</v>
+      </c>
+      <c r="B76" t="s">
         <v>134</v>
-      </c>
-      <c r="B76" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" t="s">
         <v>136</v>
-      </c>
-      <c r="B77" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" t="s">
         <v>140</v>
-      </c>
-      <c r="B80" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>141</v>
+      </c>
+      <c r="B81" t="s">
         <v>142</v>
-      </c>
-      <c r="B81" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" t="s">
         <v>144</v>
-      </c>
-      <c r="B82" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>145</v>
+      </c>
+      <c r="B83" t="s">
         <v>146</v>
-      </c>
-      <c r="B83" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>147</v>
+      </c>
+      <c r="B84" t="s">
         <v>148</v>
-      </c>
-      <c r="B84" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B86" t="s">
         <v>151</v>
-      </c>
-      <c r="B86" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" t="s">
         <v>153</v>
-      </c>
-      <c r="B87" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" t="s">
         <v>155</v>
-      </c>
-      <c r="B88" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" t="s">
         <v>157</v>
-      </c>
-      <c r="B89" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" t="s">
         <v>159</v>
-      </c>
-      <c r="B90" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>160</v>
+      </c>
+      <c r="B91" t="s">
         <v>161</v>
-      </c>
-      <c r="B91" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" t="s">
         <v>163</v>
-      </c>
-      <c r="B92" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>164</v>
+      </c>
+      <c r="B93" t="s">
         <v>165</v>
-      </c>
-      <c r="B93" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B94" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B95" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>169</v>
+      </c>
+      <c r="B97" t="s">
         <v>170</v>
-      </c>
-      <c r="B97" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>172</v>
+      </c>
+      <c r="B99" t="s">
         <v>173</v>
-      </c>
-      <c r="B99" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>174</v>
+      </c>
+      <c r="B100" t="s">
         <v>175</v>
-      </c>
-      <c r="B100" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" t="s">
         <v>177</v>
-      </c>
-      <c r="B101" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B103" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B104" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B109" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B110" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B112" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B113" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B114" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B117" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B118" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B119" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B120" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B121" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B124" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B125" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B127" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B128" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B130" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B131" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B134" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B140" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B147" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B148" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B153" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
-        <v>262</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>260</v>
+      </c>
+      <c r="B155" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
